--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/152.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/152.xlsx
@@ -426,13 +426,13 @@
         <v>-12.18123256965745</v>
       </c>
       <c r="E2">
-        <v>-11.3676537676762</v>
+        <v>-9.494196899858927</v>
       </c>
       <c r="F2">
-        <v>-5.204916669055962</v>
+        <v>-6.042958574752763</v>
       </c>
       <c r="G2">
-        <v>-14.68471715795695</v>
+        <v>-14.80318894358226</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.53115882718023</v>
       </c>
       <c r="E3">
-        <v>-11.49903385558673</v>
+        <v>-10.05129882923055</v>
       </c>
       <c r="F3">
-        <v>-5.137113140402016</v>
+        <v>-5.63778502559326</v>
       </c>
       <c r="G3">
-        <v>-15.43887312117972</v>
+        <v>-14.56061643674641</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.79056072915379</v>
       </c>
       <c r="E4">
-        <v>-11.77967244679008</v>
+        <v>-10.52029929678295</v>
       </c>
       <c r="F4">
-        <v>-5.182050415269084</v>
+        <v>-5.428986738043617</v>
       </c>
       <c r="G4">
-        <v>-15.15537885966526</v>
+        <v>-14.72263167307633</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.89161145114209</v>
       </c>
       <c r="E5">
-        <v>-13.21782522214603</v>
+        <v>-11.35943005887827</v>
       </c>
       <c r="F5">
-        <v>-5.12729615831144</v>
+        <v>-5.251939773043278</v>
       </c>
       <c r="G5">
-        <v>-15.29894870899876</v>
+        <v>-15.1307795416341</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.81307872817197</v>
       </c>
       <c r="E6">
-        <v>-13.35144237621635</v>
+        <v>-11.16073873331773</v>
       </c>
       <c r="F6">
-        <v>-5.039369100341286</v>
+        <v>-5.30151507699862</v>
       </c>
       <c r="G6">
-        <v>-15.37931730926502</v>
+        <v>-14.84608107180732</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.54749224817225</v>
       </c>
       <c r="E7">
-        <v>-14.87567238551011</v>
+        <v>-13.13800181081283</v>
       </c>
       <c r="F7">
-        <v>-4.335106873461799</v>
+        <v>-5.047801880501785</v>
       </c>
       <c r="G7">
-        <v>-16.04911142558369</v>
+        <v>-14.56392062685677</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.09840987676201</v>
       </c>
       <c r="E8">
-        <v>-14.91377496581064</v>
+        <v>-14.19562238683023</v>
       </c>
       <c r="F8">
-        <v>-4.617796361708562</v>
+        <v>-5.086700357002444</v>
       </c>
       <c r="G8">
-        <v>-15.58489076179657</v>
+        <v>-14.55795864728326</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-11.48657639388635</v>
       </c>
       <c r="E9">
-        <v>-15.82114530272755</v>
+        <v>-13.79816728012502</v>
       </c>
       <c r="F9">
-        <v>-4.309463103773336</v>
+        <v>-4.673312716676782</v>
       </c>
       <c r="G9">
-        <v>-15.04035891912048</v>
+        <v>-14.35085122367267</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-10.74747745006096</v>
       </c>
       <c r="E10">
-        <v>-15.91887882876109</v>
+        <v>-16.00847468700285</v>
       </c>
       <c r="F10">
-        <v>-4.268531813666206</v>
+        <v>-4.465332027753702</v>
       </c>
       <c r="G10">
-        <v>-15.25751344314609</v>
+        <v>-13.28767965764607</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.922446563841545</v>
       </c>
       <c r="E11">
-        <v>-16.28936234427662</v>
+        <v>-16.82106859141323</v>
       </c>
       <c r="F11">
-        <v>-4.191351994379973</v>
+        <v>-5.037200434480757</v>
       </c>
       <c r="G11">
-        <v>-14.76074798332162</v>
+        <v>-14.13501575071395</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.07317863067237</v>
       </c>
       <c r="E12">
-        <v>-16.74509891146055</v>
+        <v>-15.66280268057535</v>
       </c>
       <c r="F12">
-        <v>-4.252187296441569</v>
+        <v>-4.686247673671496</v>
       </c>
       <c r="G12">
-        <v>-14.55495632955637</v>
+        <v>-13.30852853943478</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-8.248443628399118</v>
       </c>
       <c r="E13">
-        <v>-17.68347118143397</v>
+        <v>-16.87874776484893</v>
       </c>
       <c r="F13">
-        <v>-4.039705259051677</v>
+        <v>-4.160231059424198</v>
       </c>
       <c r="G13">
-        <v>-13.92545889520924</v>
+        <v>-12.29131376256976</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-7.517235049559623</v>
       </c>
       <c r="E14">
-        <v>-18.9906061468</v>
+        <v>-19.11956350111643</v>
       </c>
       <c r="F14">
-        <v>-3.714110481176914</v>
+        <v>-4.40404526545758</v>
       </c>
       <c r="G14">
-        <v>-13.59392262823216</v>
+        <v>-11.91569592455233</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.916438220258052</v>
       </c>
       <c r="E15">
-        <v>-19.28801820572776</v>
+        <v>-20.29211221897451</v>
       </c>
       <c r="F15">
-        <v>-3.237456280462439</v>
+        <v>-4.150900328999065</v>
       </c>
       <c r="G15">
-        <v>-12.46943815614578</v>
+        <v>-11.88634211648154</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.493417373467307</v>
       </c>
       <c r="E16">
-        <v>-19.72324078565695</v>
+        <v>-18.61518206614211</v>
       </c>
       <c r="F16">
-        <v>-3.235090463160044</v>
+        <v>-4.268132540578057</v>
       </c>
       <c r="G16">
-        <v>-12.7070937524748</v>
+        <v>-10.43572390871571</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-6.25349041494349</v>
       </c>
       <c r="E17">
-        <v>-20.92463588294388</v>
+        <v>-19.82105582422263</v>
       </c>
       <c r="F17">
-        <v>-2.928386603906124</v>
+        <v>-3.174457282744731</v>
       </c>
       <c r="G17">
-        <v>-12.09109034179089</v>
+        <v>-10.22631306757039</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.205972704234196</v>
       </c>
       <c r="E18">
-        <v>-21.07172524718702</v>
+        <v>-20.80710839702281</v>
       </c>
       <c r="F18">
-        <v>-2.79992752891699</v>
+        <v>-3.026767658499607</v>
       </c>
       <c r="G18">
-        <v>-11.5296733329699</v>
+        <v>-10.02551871424017</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.318352399762055</v>
       </c>
       <c r="E19">
-        <v>-22.22238332169201</v>
+        <v>-22.19772125224624</v>
       </c>
       <c r="F19">
-        <v>-2.268377420418993</v>
+        <v>-3.164401730842148</v>
       </c>
       <c r="G19">
-        <v>-11.11599660608447</v>
+        <v>-9.41030935917364</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.560372967170474</v>
       </c>
       <c r="E20">
-        <v>-22.36285658540994</v>
+        <v>-22.23068401454807</v>
       </c>
       <c r="F20">
-        <v>-1.794463459072979</v>
+        <v>-2.738977912153809</v>
       </c>
       <c r="G20">
-        <v>-11.32551572754125</v>
+        <v>-8.813924372193647</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-6.871803207824094</v>
       </c>
       <c r="E21">
-        <v>-24.08930107304221</v>
+        <v>-22.93978870246115</v>
       </c>
       <c r="F21">
-        <v>-1.759261157923611</v>
+        <v>-2.547382330458102</v>
       </c>
       <c r="G21">
-        <v>-11.00333914506249</v>
+        <v>-9.087515907041707</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.202818999692973</v>
       </c>
       <c r="E22">
-        <v>-24.38728371969493</v>
+        <v>-22.43712808760975</v>
       </c>
       <c r="F22">
-        <v>-1.183356116842714</v>
+        <v>-2.069763081719366</v>
       </c>
       <c r="G22">
-        <v>-11.29383225216325</v>
+        <v>-9.313496917062224</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.498546082371978</v>
       </c>
       <c r="E23">
-        <v>-24.9383899494804</v>
+        <v>-23.57751105459133</v>
       </c>
       <c r="F23">
-        <v>-1.20373064148197</v>
+        <v>-1.759756521630485</v>
       </c>
       <c r="G23">
-        <v>-10.46886096524454</v>
+        <v>-8.756729399190966</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-7.718004985867524</v>
       </c>
       <c r="E24">
-        <v>-25.09358075372326</v>
+        <v>-23.89635185252339</v>
       </c>
       <c r="F24">
-        <v>-0.9683492156090878</v>
+        <v>-0.8702332385845004</v>
       </c>
       <c r="G24">
-        <v>-10.88935935175206</v>
+        <v>-10.69007107911762</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-7.831323357688928</v>
       </c>
       <c r="E25">
-        <v>-25.76072007300727</v>
+        <v>-23.46955676272248</v>
       </c>
       <c r="F25">
-        <v>-0.7085607725801208</v>
+        <v>-1.567480021929678</v>
       </c>
       <c r="G25">
-        <v>-10.90735685200561</v>
+        <v>-10.14230723320548</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-7.818156350174787</v>
       </c>
       <c r="E26">
-        <v>-26.04733624990074</v>
+        <v>-24.89367579712866</v>
       </c>
       <c r="F26">
-        <v>-0.5963857439952203</v>
+        <v>-1.09836147947847</v>
       </c>
       <c r="G26">
-        <v>-10.25668733554617</v>
+        <v>-10.55569193137213</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-7.679076587818434</v>
       </c>
       <c r="E27">
-        <v>-25.57032038335477</v>
+        <v>-25.54836634136558</v>
       </c>
       <c r="F27">
-        <v>-0.3707243812267873</v>
+        <v>-1.954158612086876</v>
       </c>
       <c r="G27">
-        <v>-10.97004787112036</v>
+        <v>-10.65859432069787</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.418793428142707</v>
       </c>
       <c r="E28">
-        <v>-25.96797474291632</v>
+        <v>-26.07748682984381</v>
       </c>
       <c r="F28">
-        <v>-0.5223388102263752</v>
+        <v>-1.312946741704071</v>
       </c>
       <c r="G28">
-        <v>-11.39614730282985</v>
+        <v>-9.6524602290391</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.066384289353112</v>
       </c>
       <c r="E29">
-        <v>-26.3746226518571</v>
+        <v>-25.51909881385401</v>
       </c>
       <c r="F29">
-        <v>-0.5825636055121076</v>
+        <v>-1.142676650426035</v>
       </c>
       <c r="G29">
-        <v>-11.08857215629063</v>
+        <v>-10.28818378129528</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.64758925698403</v>
       </c>
       <c r="E30">
-        <v>-25.71769051298638</v>
+        <v>-25.43863688768572</v>
       </c>
       <c r="F30">
-        <v>-0.3666645525856669</v>
+        <v>-0.5435425306358341</v>
       </c>
       <c r="G30">
-        <v>-10.96086045075392</v>
+        <v>-10.38775573073819</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.203943344467367</v>
       </c>
       <c r="E31">
-        <v>-26.12567885023343</v>
+        <v>-23.99240078622607</v>
       </c>
       <c r="F31">
-        <v>-0.4524494524521809</v>
+        <v>-1.519358502766249</v>
       </c>
       <c r="G31">
-        <v>-11.7748790201072</v>
+        <v>-9.942238029839901</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.762799702648611</v>
       </c>
       <c r="E32">
-        <v>-26.05654263755833</v>
+        <v>-24.33298278786896</v>
       </c>
       <c r="F32">
-        <v>-0.5424880189320704</v>
+        <v>-0.9274734261179463</v>
       </c>
       <c r="G32">
-        <v>-11.545879286252</v>
+        <v>-10.25707123846862</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.359429668863728</v>
       </c>
       <c r="E33">
-        <v>-25.34384234128316</v>
+        <v>-24.91001000287433</v>
       </c>
       <c r="F33">
-        <v>-0.6723023029921837</v>
+        <v>-0.9092261489690787</v>
       </c>
       <c r="G33">
-        <v>-11.01140438765561</v>
+        <v>-11.2111487500868</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.009471712641914</v>
       </c>
       <c r="E34">
-        <v>-26.75634583985966</v>
+        <v>-24.42775922037549</v>
       </c>
       <c r="F34">
-        <v>-0.8319875155972472</v>
+        <v>-1.244239464213672</v>
       </c>
       <c r="G34">
-        <v>-11.10538185433966</v>
+        <v>-9.443718757091906</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.731386343828666</v>
       </c>
       <c r="E35">
-        <v>-24.96674272524242</v>
+        <v>-24.72676983062795</v>
       </c>
       <c r="F35">
-        <v>-1.082489960040832</v>
+        <v>-1.046740936405616</v>
       </c>
       <c r="G35">
-        <v>-11.65312929414401</v>
+        <v>-10.45590670252785</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.523667134005098</v>
       </c>
       <c r="E36">
-        <v>-24.98861525469947</v>
+        <v>-23.03886265680097</v>
       </c>
       <c r="F36">
-        <v>-0.780380226402838</v>
+        <v>-0.9943342726675055</v>
       </c>
       <c r="G36">
-        <v>-10.94069734427113</v>
+        <v>-10.59545705545104</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.386645364276222</v>
       </c>
       <c r="E37">
-        <v>-23.77961684955366</v>
+        <v>-24.0068783176286</v>
       </c>
       <c r="F37">
-        <v>-0.6644278424611716</v>
+        <v>-1.547376373431137</v>
       </c>
       <c r="G37">
-        <v>-11.42967810594582</v>
+        <v>-9.394982773269474</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.31084989691961</v>
       </c>
       <c r="E38">
-        <v>-24.08103660797821</v>
+        <v>-23.96073769596444</v>
       </c>
       <c r="F38">
-        <v>-0.969649752431483</v>
+        <v>-1.027439975920388</v>
       </c>
       <c r="G38">
-        <v>-11.13885687668912</v>
+        <v>-9.874874551224501</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.286377047643712</v>
       </c>
       <c r="E39">
-        <v>-23.961068274567</v>
+        <v>-23.26687132308717</v>
       </c>
       <c r="F39">
-        <v>-0.7650140110809072</v>
+        <v>-0.8469627415050567</v>
       </c>
       <c r="G39">
-        <v>-11.29010478447172</v>
+        <v>-8.964125570298789</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.304101031582044</v>
       </c>
       <c r="E40">
-        <v>-24.47860492653361</v>
+        <v>-22.51366835528739</v>
       </c>
       <c r="F40">
-        <v>-0.7150725687335278</v>
+        <v>-1.400276546776806</v>
       </c>
       <c r="G40">
-        <v>-11.02019478021336</v>
+        <v>-10.48925047601493</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.349569984095949</v>
       </c>
       <c r="E41">
-        <v>-22.19072023143038</v>
+        <v>-22.19519436374996</v>
       </c>
       <c r="F41">
-        <v>-0.639937988564807</v>
+        <v>-1.3079251785083</v>
       </c>
       <c r="G41">
-        <v>-10.81774669121718</v>
+        <v>-9.212871695498732</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.417593764286843</v>
       </c>
       <c r="E42">
-        <v>-22.86107929573384</v>
+        <v>-20.49838421002389</v>
       </c>
       <c r="F42">
-        <v>-0.7120705652657824</v>
+        <v>-1.136225325093033</v>
       </c>
       <c r="G42">
-        <v>-10.93106695899416</v>
+        <v>-8.736668010576521</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.493513322461904</v>
       </c>
       <c r="E43">
-        <v>-21.65088537345</v>
+        <v>-22.01949862920036</v>
       </c>
       <c r="F43">
-        <v>-1.026464987487293</v>
+        <v>-1.192830983195934</v>
       </c>
       <c r="G43">
-        <v>-11.06725734104047</v>
+        <v>-9.534979372324742</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.575275045718288</v>
       </c>
       <c r="E44">
-        <v>-21.28898784465302</v>
+        <v>-20.7003043375519</v>
       </c>
       <c r="F44">
-        <v>-0.9988182254188592</v>
+        <v>-1.270019086156195</v>
       </c>
       <c r="G44">
-        <v>-10.18225282447016</v>
+        <v>-8.814052339834465</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.651243917286239</v>
       </c>
       <c r="E45">
-        <v>-21.75922911408352</v>
+        <v>-20.42609617943945</v>
       </c>
       <c r="F45">
-        <v>-1.313534882560059</v>
+        <v>-1.741075179962551</v>
       </c>
       <c r="G45">
-        <v>-10.5417533021876</v>
+        <v>-8.449150971430178</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.723915889186427</v>
       </c>
       <c r="E46">
-        <v>-21.2538514148275</v>
+        <v>-20.4162648623688</v>
       </c>
       <c r="F46">
-        <v>-0.9938049458971167</v>
+        <v>-1.235814139359798</v>
       </c>
       <c r="G46">
-        <v>-10.21624299860445</v>
+        <v>-9.178701054178676</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.786684108675809</v>
       </c>
       <c r="E47">
-        <v>-20.65617888682116</v>
+        <v>-19.27367200007146</v>
       </c>
       <c r="F47">
-        <v>-1.205841321624303</v>
+        <v>-1.981056530023179</v>
       </c>
       <c r="G47">
-        <v>-9.829344320865646</v>
+        <v>-8.147183432536041</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.846983978317073</v>
       </c>
       <c r="E48">
-        <v>-19.88062789979353</v>
+        <v>-20.10386355447565</v>
       </c>
       <c r="F48">
-        <v>-1.337507835197076</v>
+        <v>-1.64578393578151</v>
       </c>
       <c r="G48">
-        <v>-10.46411631886958</v>
+        <v>-8.911803211311883</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.90236335049962</v>
       </c>
       <c r="E49">
-        <v>-19.41841108630462</v>
+        <v>-19.15009447287615</v>
       </c>
       <c r="F49">
-        <v>-1.432505008950124</v>
+        <v>-2.12323585430488</v>
       </c>
       <c r="G49">
-        <v>-10.3999389063884</v>
+        <v>-7.962959248081017</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.963419859558538</v>
       </c>
       <c r="E50">
-        <v>-19.47642536681689</v>
+        <v>-18.57073056528282</v>
       </c>
       <c r="F50">
-        <v>-1.724027378812937</v>
+        <v>-1.681679580447021</v>
       </c>
       <c r="G50">
-        <v>-10.41801843718094</v>
+        <v>-8.329898255073719</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.030118263571485</v>
       </c>
       <c r="E51">
-        <v>-18.89064008308068</v>
+        <v>-18.34878552569289</v>
       </c>
       <c r="F51">
-        <v>-1.603133783313571</v>
+        <v>-1.87233827861016</v>
       </c>
       <c r="G51">
-        <v>-9.949108907785378</v>
+        <v>-8.378785175087886</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.111963434687829</v>
       </c>
       <c r="E52">
-        <v>-18.76554098861879</v>
+        <v>-16.84635559027206</v>
       </c>
       <c r="F52">
-        <v>-1.625552718702937</v>
+        <v>-2.382244803607813</v>
       </c>
       <c r="G52">
-        <v>-9.473728809474588</v>
+        <v>-8.008856975254529</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.209829172555895</v>
       </c>
       <c r="E53">
-        <v>-18.62616361561071</v>
+        <v>-16.83889719358143</v>
       </c>
       <c r="F53">
-        <v>-1.842226295150996</v>
+        <v>-2.142357887431104</v>
       </c>
       <c r="G53">
-        <v>-10.01480880707014</v>
+        <v>-8.060605120468532</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.326230579686794</v>
       </c>
       <c r="E54">
-        <v>-18.50450163292064</v>
+        <v>-18.32633335156286</v>
       </c>
       <c r="F54">
-        <v>-1.556889344684886</v>
+        <v>-2.372393858453721</v>
       </c>
       <c r="G54">
-        <v>-9.564917237833116</v>
+        <v>-8.164491876262112</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.461567316098285</v>
       </c>
       <c r="E55">
-        <v>-18.30802473114985</v>
+        <v>-17.02518050036096</v>
       </c>
       <c r="F55">
-        <v>-1.808747826566854</v>
+        <v>-2.65426574807392</v>
       </c>
       <c r="G55">
-        <v>-10.02745463496024</v>
+        <v>-8.558471430126197</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.610498708853017</v>
       </c>
       <c r="E56">
-        <v>-18.13210257289987</v>
+        <v>-15.8010434066075</v>
       </c>
       <c r="F56">
-        <v>-1.655127920085088</v>
+        <v>-1.788736126850023</v>
       </c>
       <c r="G56">
-        <v>-9.802369398425451</v>
+        <v>-7.786084999919149</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.773360659040984</v>
       </c>
       <c r="E57">
-        <v>-17.24917241020236</v>
+        <v>-17.71013483639113</v>
       </c>
       <c r="F57">
-        <v>-1.519304658885067</v>
+        <v>-2.614509082943961</v>
       </c>
       <c r="G57">
-        <v>-9.717612164323436</v>
+        <v>-8.398623440636289</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.939799560287573</v>
       </c>
       <c r="E58">
-        <v>-16.83968061958475</v>
+        <v>-16.04420887539738</v>
       </c>
       <c r="F58">
-        <v>-1.515826344160712</v>
+        <v>-2.553108834313655</v>
       </c>
       <c r="G58">
-        <v>-9.72638615077339</v>
+        <v>-8.513239790929251</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.110031225429084</v>
       </c>
       <c r="E59">
-        <v>-17.11318686422602</v>
+        <v>-16.89259583836438</v>
       </c>
       <c r="F59">
-        <v>-1.783121452593848</v>
+        <v>-1.938266383464167</v>
       </c>
       <c r="G59">
-        <v>-10.03389567288143</v>
+        <v>-7.851903023180051</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.271678068676775</v>
       </c>
       <c r="E60">
-        <v>-17.10200606190108</v>
+        <v>-16.30722717423688</v>
       </c>
       <c r="F60">
-        <v>-1.561327737229086</v>
+        <v>-2.046469390352645</v>
       </c>
       <c r="G60">
-        <v>-9.964041747102412</v>
+        <v>-8.553651315655372</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.426413561737242</v>
       </c>
       <c r="E61">
-        <v>-16.66376751828279</v>
+        <v>-15.34339129491833</v>
       </c>
       <c r="F61">
-        <v>-1.684979796179774</v>
+        <v>-2.199380214337614</v>
       </c>
       <c r="G61">
-        <v>-10.15069403551142</v>
+        <v>-8.687895933316934</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.563024571161695</v>
       </c>
       <c r="E62">
-        <v>-16.40188586641921</v>
+        <v>-14.83050991423161</v>
       </c>
       <c r="F62">
-        <v>-1.47102989175212</v>
+        <v>-2.167953611810206</v>
       </c>
       <c r="G62">
-        <v>-10.4355139105359</v>
+        <v>-8.711596196640803</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.686763630616699</v>
       </c>
       <c r="E63">
-        <v>-15.64364723552291</v>
+        <v>-14.96566674946454</v>
       </c>
       <c r="F63">
-        <v>-1.714579020216606</v>
+        <v>-2.252770150182847</v>
       </c>
       <c r="G63">
-        <v>-10.33958083580242</v>
+        <v>-8.328290456509592</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.790753100789105</v>
       </c>
       <c r="E64">
-        <v>-15.39557290090872</v>
+        <v>-15.76107962348981</v>
       </c>
       <c r="F64">
-        <v>-1.610556783610058</v>
+        <v>-1.888547771948141</v>
       </c>
       <c r="G64">
-        <v>-10.17457476602106</v>
+        <v>-9.933867633641757</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.885094847643061</v>
       </c>
       <c r="E65">
-        <v>-15.40075347517349</v>
+        <v>-16.75486230142109</v>
       </c>
       <c r="F65">
-        <v>-1.657565805351527</v>
+        <v>-1.907442004038595</v>
       </c>
       <c r="G65">
-        <v>-10.79198253953242</v>
+        <v>-9.377126365542976</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.968243911741738</v>
       </c>
       <c r="E66">
-        <v>-16.12456211818948</v>
+        <v>-15.26138063063942</v>
       </c>
       <c r="F66">
-        <v>-2.049174838290188</v>
+        <v>-2.307469734891907</v>
       </c>
       <c r="G66">
-        <v>-10.84318272074599</v>
+        <v>-8.551836800133</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.049879485103185</v>
       </c>
       <c r="E67">
-        <v>-15.14266668452834</v>
+        <v>-15.61237359402593</v>
       </c>
       <c r="F67">
-        <v>-1.567686285412975</v>
+        <v>-2.438836379464866</v>
       </c>
       <c r="G67">
-        <v>-10.64871128136082</v>
+        <v>-9.435938980774463</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.133245680596992</v>
       </c>
       <c r="E68">
-        <v>-14.95365270792219</v>
+        <v>-14.8286170120964</v>
       </c>
       <c r="F68">
-        <v>-1.521021036143668</v>
+        <v>-2.124142088243543</v>
       </c>
       <c r="G68">
-        <v>-10.61834357582816</v>
+        <v>-10.06410587977924</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.222241479142085</v>
       </c>
       <c r="E69">
-        <v>-15.46244487657998</v>
+        <v>-14.03626991497432</v>
       </c>
       <c r="F69">
-        <v>-1.626610543876312</v>
+        <v>-2.267116645231932</v>
       </c>
       <c r="G69">
-        <v>-10.71994988263793</v>
+        <v>-9.173418287467969</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.322328205111919</v>
       </c>
       <c r="E70">
-        <v>-15.94421111236</v>
+        <v>-14.47002979779903</v>
       </c>
       <c r="F70">
-        <v>-1.736188640653436</v>
+        <v>-2.947364501104261</v>
       </c>
       <c r="G70">
-        <v>-10.93896157806618</v>
+        <v>-10.20359717071435</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.429866502448262</v>
       </c>
       <c r="E71">
-        <v>-16.05687048872283</v>
+        <v>-15.38447813958992</v>
       </c>
       <c r="F71">
-        <v>-1.772977265379165</v>
+        <v>-2.248177681301727</v>
       </c>
       <c r="G71">
-        <v>-10.61923934931389</v>
+        <v>-9.279857833634797</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.551804404610841</v>
       </c>
       <c r="E72">
-        <v>-16.32256511570086</v>
+        <v>-14.17230074569073</v>
       </c>
       <c r="F72">
-        <v>-1.627541628837059</v>
+        <v>-2.799292171119043</v>
       </c>
       <c r="G72">
-        <v>-10.52019239532049</v>
+        <v>-10.02484606382048</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.680213430911071</v>
       </c>
       <c r="E73">
-        <v>-16.26565125437246</v>
+        <v>-16.1246345737736</v>
       </c>
       <c r="F73">
-        <v>-1.614680396541194</v>
+        <v>-2.179279050941281</v>
       </c>
       <c r="G73">
-        <v>-10.4162990770838</v>
+        <v>-8.907681997033221</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.822065624627119</v>
       </c>
       <c r="E74">
-        <v>-16.04729729467061</v>
+        <v>-15.39974362546978</v>
       </c>
       <c r="F74">
-        <v>-1.68583384297206</v>
+        <v>-2.139877755427122</v>
       </c>
       <c r="G74">
-        <v>-9.726294276569726</v>
+        <v>-8.974438449660123</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.966023203326079</v>
       </c>
       <c r="E75">
-        <v>-16.71032928802966</v>
+        <v>-14.26036597971789</v>
       </c>
       <c r="F75">
-        <v>-2.092056105263507</v>
+        <v>-1.945489747216579</v>
       </c>
       <c r="G75">
-        <v>-10.01011009779702</v>
+        <v>-9.081038775683362</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-8.117261863674088</v>
       </c>
       <c r="E76">
-        <v>-16.71994776682195</v>
+        <v>-17.03385705655965</v>
       </c>
       <c r="F76">
-        <v>-1.753176799350049</v>
+        <v>-2.542972930773001</v>
       </c>
       <c r="G76">
-        <v>-10.09603544677419</v>
+        <v>-10.16031785834527</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-8.262141104408627</v>
       </c>
       <c r="E77">
-        <v>-16.97191206060873</v>
+        <v>-15.93099249673161</v>
       </c>
       <c r="F77">
-        <v>-1.764757375641186</v>
+        <v>-2.733991140388956</v>
       </c>
       <c r="G77">
-        <v>-9.639853775807714</v>
+        <v>-8.420437001563478</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-8.404953076873539</v>
       </c>
       <c r="E78">
-        <v>-17.53112425886793</v>
+        <v>-15.72533637814727</v>
       </c>
       <c r="F78">
-        <v>-2.077823096548606</v>
+        <v>-2.680246663295324</v>
       </c>
       <c r="G78">
-        <v>-9.846938230867389</v>
+        <v>-8.520806287845332</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-8.532214993425255</v>
       </c>
       <c r="E79">
-        <v>-17.68651431596713</v>
+        <v>-17.20954826263524</v>
       </c>
       <c r="F79">
-        <v>-2.039623762135909</v>
+        <v>-3.084591845052027</v>
       </c>
       <c r="G79">
-        <v>-10.10069478138861</v>
+        <v>-9.219913196965301</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-8.646678829292275</v>
       </c>
       <c r="E80">
-        <v>-18.07720841097889</v>
+        <v>-16.97431215183279</v>
       </c>
       <c r="F80">
-        <v>-2.192498137955155</v>
+        <v>-2.870593895315011</v>
       </c>
       <c r="G80">
-        <v>-8.988869262078561</v>
+        <v>-10.08275634312312</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-8.738755110578699</v>
       </c>
       <c r="E81">
-        <v>-18.49246042053424</v>
+        <v>-19.27355425974726</v>
       </c>
       <c r="F81">
-        <v>-2.309133925004131</v>
+        <v>-3.159923576662614</v>
       </c>
       <c r="G81">
-        <v>-8.520848943725605</v>
+        <v>-8.848961256005397</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-8.808024623537444</v>
       </c>
       <c r="E82">
-        <v>-19.80177811037197</v>
+        <v>-17.55014384970014</v>
       </c>
       <c r="F82">
-        <v>-2.42023124759799</v>
+        <v>-2.888552072240302</v>
       </c>
       <c r="G82">
-        <v>-9.205521759205576</v>
+        <v>-8.918185187245003</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-8.85263734352481</v>
       </c>
       <c r="E83">
-        <v>-19.75834551616441</v>
+        <v>-19.86925690156027</v>
       </c>
       <c r="F83">
-        <v>-2.503128458698344</v>
+        <v>-2.300967050779931</v>
       </c>
       <c r="G83">
-        <v>-9.754256846699313</v>
+        <v>-9.188124722497401</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-8.87013024431349</v>
       </c>
       <c r="E84">
-        <v>-21.05137881347056</v>
+        <v>-20.73073568288345</v>
       </c>
       <c r="F84">
-        <v>-2.865700729066674</v>
+        <v>-3.077216890064903</v>
       </c>
       <c r="G84">
-        <v>-9.580870537055135</v>
+        <v>-7.945877208642547</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-8.867630879052159</v>
       </c>
       <c r="E85">
-        <v>-23.08950911010275</v>
+        <v>-21.09153732097058</v>
       </c>
       <c r="F85">
-        <v>-2.89900275539402</v>
+        <v>-3.150985492386407</v>
       </c>
       <c r="G85">
-        <v>-8.676998996518019</v>
+        <v>-7.346758964103537</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-8.841686052579924</v>
       </c>
       <c r="E86">
-        <v>-23.20341834529169</v>
+        <v>-22.47278982042015</v>
       </c>
       <c r="F86">
-        <v>-2.362212394705912</v>
+        <v>-3.421430053684987</v>
       </c>
       <c r="G86">
-        <v>-8.751512256911449</v>
+        <v>-8.785810865872325</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-8.806459840997043</v>
       </c>
       <c r="E87">
-        <v>-24.32459605400675</v>
+        <v>-23.90151884136614</v>
       </c>
       <c r="F87">
-        <v>-2.85884930227812</v>
+        <v>-3.267231946756068</v>
       </c>
       <c r="G87">
-        <v>-8.996104355617137</v>
+        <v>-7.69224534454059</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-8.76035328877184</v>
       </c>
       <c r="E88">
-        <v>-25.42881009908908</v>
+        <v>-23.97050561439899</v>
       </c>
       <c r="F88">
-        <v>-2.770919759205758</v>
+        <v>-3.183476547026412</v>
       </c>
       <c r="G88">
-        <v>-8.38254217377345</v>
+        <v>-7.626135292560898</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-8.723889921393596</v>
       </c>
       <c r="E89">
-        <v>-27.38042389980473</v>
+        <v>-26.44397170281056</v>
       </c>
       <c r="F89">
-        <v>-2.526563800890945</v>
+        <v>-3.679060599629661</v>
       </c>
       <c r="G89">
-        <v>-8.394984565926865</v>
+        <v>-8.202816544076425</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-8.698484007540445</v>
       </c>
       <c r="E90">
-        <v>-28.40317069748907</v>
+        <v>-27.85018515099042</v>
       </c>
       <c r="F90">
-        <v>-2.83494096229852</v>
+        <v>-3.694970223967828</v>
       </c>
       <c r="G90">
-        <v>-8.582037163366129</v>
+        <v>-8.243342911557127</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.707759493918251</v>
       </c>
       <c r="E91">
-        <v>-30.46725594289623</v>
+        <v>-29.50169697921775</v>
       </c>
       <c r="F91">
-        <v>-3.068086624551247</v>
+        <v>-3.464180438608664</v>
       </c>
       <c r="G91">
-        <v>-8.8923193176919</v>
+        <v>-8.122912236660827</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.751975495453985</v>
       </c>
       <c r="E92">
-        <v>-31.93248672858104</v>
+        <v>-31.31677502436515</v>
       </c>
       <c r="F92">
-        <v>-2.975109010526225</v>
+        <v>-3.272627103650501</v>
       </c>
       <c r="G92">
-        <v>-9.188315033347848</v>
+        <v>-8.016078943906868</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.851721163377718</v>
       </c>
       <c r="E93">
-        <v>-33.87149099342234</v>
+        <v>-33.44571481027316</v>
       </c>
       <c r="F93">
-        <v>-3.051721398141539</v>
+        <v>-3.656704620162908</v>
       </c>
       <c r="G93">
-        <v>-8.982293694073434</v>
+        <v>-7.424520633840817</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.002124850105599</v>
       </c>
       <c r="E94">
-        <v>-35.76502258651561</v>
+        <v>-35.81776119480894</v>
       </c>
       <c r="F94">
-        <v>-3.081875628338247</v>
+        <v>-3.869342390624527</v>
       </c>
       <c r="G94">
-        <v>-9.280028457155888</v>
+        <v>-9.204104271491897</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.212797535538622</v>
       </c>
       <c r="E95">
-        <v>-38.52281344397278</v>
+        <v>-38.46937518644526</v>
       </c>
       <c r="F95">
-        <v>-2.925707663725471</v>
+        <v>-3.63232908096813</v>
       </c>
       <c r="G95">
-        <v>-9.307633374135497</v>
+        <v>-9.365953806133067</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.476213487303214</v>
       </c>
       <c r="E96">
-        <v>-39.30044073633293</v>
+        <v>-40.46514160873571</v>
       </c>
       <c r="F96">
-        <v>-3.080872475413457</v>
+        <v>-3.839198929204056</v>
       </c>
       <c r="G96">
-        <v>-9.454599287783024</v>
+        <v>-9.836074106284068</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.782943349319527</v>
       </c>
       <c r="E97">
-        <v>-41.76119539820497</v>
+        <v>-41.40875558737301</v>
       </c>
       <c r="F97">
-        <v>-2.835081784756996</v>
+        <v>-3.831029569877647</v>
       </c>
       <c r="G97">
-        <v>-10.27814980576649</v>
+        <v>-8.835737933120836</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.12587536507192</v>
       </c>
       <c r="E98">
-        <v>-44.65460046676984</v>
+        <v>-43.73506438443133</v>
       </c>
       <c r="F98">
-        <v>-2.988250231004236</v>
+        <v>-3.668171710119862</v>
       </c>
       <c r="G98">
-        <v>-10.30537081982365</v>
+        <v>-9.313562541493413</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.47539089882979</v>
       </c>
       <c r="E99">
-        <v>-46.52329337993104</v>
+        <v>-46.53028307956188</v>
       </c>
       <c r="F99">
-        <v>-2.900357136097597</v>
+        <v>-4.127081452698969</v>
       </c>
       <c r="G99">
-        <v>-10.15308604602826</v>
+        <v>-9.357130601359719</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.8306937933706</v>
       </c>
       <c r="E100">
-        <v>-49.17577231010283</v>
+        <v>-48.25440672426522</v>
       </c>
       <c r="F100">
-        <v>-2.817316617436558</v>
+        <v>-3.621613320245515</v>
       </c>
       <c r="G100">
-        <v>-10.99721310441101</v>
+        <v>-11.13734423355021</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-11.14282596484063</v>
       </c>
       <c r="E101">
-        <v>-51.63293023149428</v>
+        <v>-51.07500751620876</v>
       </c>
       <c r="F101">
-        <v>-2.922329581456854</v>
+        <v>-3.986456145664918</v>
       </c>
       <c r="G101">
-        <v>-11.44677983271365</v>
+        <v>-11.8014897269543</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-11.43416286844269</v>
       </c>
       <c r="E102">
-        <v>-53.25391788067292</v>
+        <v>-53.82709023217926</v>
       </c>
       <c r="F102">
-        <v>-2.837610790437743</v>
+        <v>-3.945814784148769</v>
       </c>
       <c r="G102">
-        <v>-11.55015799916551</v>
+        <v>-11.29692972531537</v>
       </c>
     </row>
   </sheetData>
